--- a/financial-normalizer/data/样本_科目余额表.xlsx
+++ b/financial-normalizer/data/样本_科目余额表.xlsx
@@ -37,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +45,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,83 +417,123 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:P24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="6" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>科目编码</t>
+          <t>企业主体名称</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>币种</t>
+          <t>查询区间</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>科目编号</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>科目名称</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>一级科目</t>
-        </is>
-      </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>二级科目</t>
+          <t>核算类型</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>三级科目</t>
+          <t>核算编号</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>期初借方余额</t>
+          <t>核算名称</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>期初贷方余额</t>
+          <t>数据类型</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>本期借方发生额</t>
+          <t>方向</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>本期贷方发生额</t>
+          <t>本位币期初</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>期末借方余额</t>
+          <t>本位币借方</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>期末贷方余额</t>
+          <t>本位币贷方</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>本位币期末</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>科目全路径</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>损益结转金额</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>标准1级科目</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>1001</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>样本科技有限公司</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>人民币</t>
+          <t>2025-01~2025-12</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>库存现金</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -511,37 +543,57 @@
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
-      <c r="G2" t="n">
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>本位币</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>借</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
         <v>5000</v>
       </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
+      <c r="K2" t="n">
         <v>20000</v>
       </c>
-      <c r="J2" t="n">
+      <c r="L2" t="n">
         <v>18000</v>
       </c>
-      <c r="K2" t="n">
+      <c r="M2" t="n">
         <v>7000</v>
       </c>
-      <c r="L2" t="n">
-        <v>0</v>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>库存现金</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>库存现金</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>1002</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>样本科技有限公司</t>
+        </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>人民币</t>
+          <t>2025-01~2025-12</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>银行存款</t>
+          <t>1002</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -551,423 +603,1337 @@
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
-      <c r="G3" t="n">
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>本位币</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>借</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
         <v>500000</v>
       </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
+      <c r="K3" t="n">
         <v>1500000</v>
       </c>
-      <c r="J3" t="n">
+      <c r="L3" t="n">
         <v>1400000</v>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" t="n">
         <v>600000</v>
       </c>
-      <c r="L3" t="n">
-        <v>0</v>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>银行存款</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>银行存款</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>1122</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>样本科技有限公司</t>
+        </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>人民币</t>
+          <t>2025-01~2025-12</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>100201</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>工商银行</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>银行账户</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0011-1101021119900266558</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>工商银行北京分行人民币活期户</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>本位币</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>借</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>10000</v>
+      </c>
+      <c r="K4" t="n">
+        <v>800000</v>
+      </c>
+      <c r="L4" t="n">
+        <v>750000</v>
+      </c>
+      <c r="M4" t="n">
+        <v>60000</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>银行存款/工商银行</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>银行存款</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>样本科技有限公司</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2025-01~2025-12</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1122</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>应收账款</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>应收账款</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="n">
-        <v>300000</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>500000</v>
-      </c>
-      <c r="J4" t="n">
-        <v>400000</v>
-      </c>
-      <c r="K4" t="n">
-        <v>400000</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>1123</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>人民币</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>预付账款</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>预付账款</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
-      <c r="G5" t="n">
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>本位币</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>借</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>250000</v>
+      </c>
+      <c r="L5" t="n">
+        <v>100000</v>
+      </c>
+      <c r="M5" t="n">
+        <v>150000</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>应收账款</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>应收账款</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>样本科技有限公司</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2025-01~2025-12</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>112201</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>客户A</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>客户</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0001-001</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>北京客户A有限公司</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>本位币</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>借</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>150000</v>
+      </c>
+      <c r="L6" t="n">
         <v>50000</v>
       </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
+      <c r="M6" t="n">
         <v>100000</v>
       </c>
-      <c r="J5" t="n">
-        <v>80000</v>
-      </c>
-      <c r="K5" t="n">
-        <v>70000</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>1221</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>人民币</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>应收账款/客户A</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>应收账款</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>样本科技有限公司</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2025-01~2025-12</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>112202</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>客户B</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>客户</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0001-002</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>上海客户B有限公司</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>本位币</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>借</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>100000</v>
+      </c>
+      <c r="L7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="M7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>应收账款/客户B</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>应收账款</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>样本科技有限公司</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2025-01~2025-12</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1221</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
         <is>
           <t>其他应收款</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>其他应收款</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="n">
-        <v>20000</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>50000</v>
-      </c>
-      <c r="J6" t="n">
-        <v>45000</v>
-      </c>
-      <c r="K6" t="n">
-        <v>25000</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>1403</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>人民币</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>原材料</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>原材料</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="n">
-        <v>150000</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>300000</v>
-      </c>
-      <c r="J7" t="n">
-        <v>250000</v>
-      </c>
-      <c r="K7" t="n">
-        <v>200000</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>1405</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>人民币</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>库存商品</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>库存商品</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
-      <c r="G8" t="n">
-        <v>200000</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>400000</v>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>本位币</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>借</t>
+        </is>
       </c>
       <c r="J8" t="n">
-        <v>350000</v>
+        <v>5000</v>
       </c>
       <c r="K8" t="n">
-        <v>250000</v>
+        <v>30000</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>20000</v>
+      </c>
+      <c r="M8" t="n">
+        <v>15000</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>其他应收款</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>其他应收款</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
-        <v>1601</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>样本科技有限公司</t>
+        </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>人民币</t>
+          <t>2025-01~2025-12</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>固定资产</t>
+          <t>1403</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>固定资产</t>
+          <t>原材料</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
-      <c r="G9" t="n">
-        <v>800000</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>本位币</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>借</t>
+        </is>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>80000</v>
       </c>
       <c r="K9" t="n">
-        <v>800000</v>
+        <v>500000</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>480000</v>
+      </c>
+      <c r="M9" t="n">
+        <v>100000</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>原材料</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>存货</t>
+        </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
-        <v>2001</v>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>样本科技有限公司</t>
+        </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>人民币</t>
+          <t>2025-01~2025-12</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>短期借款</t>
+          <t>1405</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>短期借款</t>
+          <t>库存商品</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>200000</v>
-      </c>
-      <c r="I10" t="n">
-        <v>300000</v>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>本位币</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>借</t>
+        </is>
       </c>
       <c r="J10" t="n">
-        <v>200000</v>
+        <v>120000</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>800000</v>
       </c>
       <c r="L10" t="n">
-        <v>300000</v>
+        <v>760000</v>
+      </c>
+      <c r="M10" t="n">
+        <v>160000</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>库存商品</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>存货</t>
+        </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
-        <v>2202</v>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>样本科技有限公司</t>
+        </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>人民币</t>
+          <t>2025-01~2025-12</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>应付账款</t>
+          <t>1601</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>应付账款</t>
+          <t>固定资产</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>250000</v>
-      </c>
-      <c r="I11" t="n">
-        <v>100000</v>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>本位币</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>借</t>
+        </is>
       </c>
       <c r="J11" t="n">
-        <v>120000</v>
+        <v>1500000</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="L11" t="n">
-        <v>270000</v>
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1700000</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>固定资产</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>固定资产</t>
+        </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
-        <v>4001</v>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>样本科技有限公司</t>
+        </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>人民币</t>
+          <t>2025-01~2025-12</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>实收资本</t>
+          <t>1602</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>实收资本</t>
+          <t>累计折旧</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>本位币</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>贷</t>
+        </is>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>-300000</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>1000000</v>
+        <v>80000</v>
+      </c>
+      <c r="M12" t="n">
+        <v>-380000</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>累计折旧</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>固定资产</t>
+        </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="n">
-        <v>4104</v>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>样本科技有限公司</t>
+        </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>人民币</t>
+          <t>2025-01~2025-12</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>未分配利润</t>
+          <t>2202</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>未分配利润</t>
+          <t>应付账款</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>575000</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>本位币</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>贷</t>
+        </is>
       </c>
       <c r="J13" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="K13" t="n">
+        <v>80000</v>
+      </c>
+      <c r="L13" t="n">
+        <v>200000</v>
+      </c>
+      <c r="M13" t="n">
+        <v>-220000</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>应付账款</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>应付账款</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>样本科技有限公司</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2025-01~2025-12</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2211</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>应付职工薪酬</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>本位币</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>贷</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>-50000</v>
+      </c>
+      <c r="K14" t="n">
+        <v>200000</v>
+      </c>
+      <c r="L14" t="n">
+        <v>220000</v>
+      </c>
+      <c r="M14" t="n">
+        <v>-70000</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>应付职工薪酬</t>
+        </is>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>应付职工薪酬</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>样本科技有限公司</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2025-01~2025-12</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2221</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>应交税费</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>本位币</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>贷</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>-30000</v>
+      </c>
+      <c r="K15" t="n">
         <v>50000</v>
       </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>625000</v>
+      <c r="L15" t="n">
+        <v>60000</v>
+      </c>
+      <c r="M15" t="n">
+        <v>-40000</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>应交税费</t>
+        </is>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>应交税费</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>样本科技有限公司</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2025-01~2025-12</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>4001</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>实收资本</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>本位币</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>贷</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>-1000000</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>-1000000</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>实收资本</t>
+        </is>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>实收资本</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>样本科技有限公司</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2025-01~2025-12</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>盈余公积</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>本位币</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>贷</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>-50000</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>10000</v>
+      </c>
+      <c r="M17" t="n">
+        <v>-60000</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>盈余公积</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>盈余公积</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>样本科技有限公司</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2025-01~2025-12</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>本年利润</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>本位币</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>贷</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>350000</v>
+      </c>
+      <c r="M18" t="n">
+        <v>-350000</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>本年利润</t>
+        </is>
+      </c>
+      <c r="O18" t="n">
+        <v>350000</v>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>本年利润</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>样本科技有限公司</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2025-01~2025-12</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>410399</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>未分配利润</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>本位币</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>贷</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>-200000</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>50000</v>
+      </c>
+      <c r="M19" t="n">
+        <v>-250000</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>利润分配/未分配利润</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
+        <v>50000</v>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>利润分配</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>样本科技有限公司</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2025-01~2025-12</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>6001</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>主营业务收入</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>本位币</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>贷</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="M20" t="n">
+        <v>-1500000</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>主营业务收入</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>主营业务收入</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>样本科技有限公司</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2025-01~2025-12</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>6401</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>主营业务成本</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>本位币</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>借</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1100000</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1100000</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>主营业务成本</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>1100000</v>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>主营业务成本</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>样本科技有限公司</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2025-01~2025-12</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>6601</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>销售费用</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>本位币</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>借</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>50000</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>销售费用</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
+        <v>50000</v>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>销售费用</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>样本科技有限公司</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2025-01~2025-12</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>6602</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>管理费用</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>本位币</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>借</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>100000</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>100000</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>管理费用</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>100000</v>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>管理费用</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>样本科技有限公司</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2025-01~2025-12</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>6603</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>财务费用</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>本位币</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>借</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>50000</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>财务费用</t>
+        </is>
+      </c>
+      <c r="O24" t="n">
+        <v>50000</v>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>财务费用</t>
+        </is>
       </c>
     </row>
   </sheetData>
